--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260812.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260812.xlsx
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>504,385,458</t>
+          <t>66,432,983</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>66,432,983</t>
+          <t>504,385,458</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>32,936,330</t>
+          <t>11,083,402</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>11,083,402</t>
+          <t>32,936,330</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
